--- a/code/api-autotest-tool/case/case.xlsx
+++ b/code/api-autotest-tool/case/case.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2087\Desktop\REPO\pw-z.github.io\code\api-autotest-tool\case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA06857-94B8-442C-9BA2-F9EAA454CC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6FDB2C-791B-4ED9-8FAF-1787843FDC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="30936" windowHeight="17040" tabRatio="780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="87">
   <si>
     <t>Note</t>
   </si>
@@ -36,7 +36,7 @@
     <t>CaseStep</t>
   </si>
   <si>
-    <t>是否执行</t>
+    <t>Run?</t>
   </si>
   <si>
     <t>Delay</t>
@@ -66,7 +66,7 @@
     <t>expectedData</t>
   </si>
   <si>
-    <t>responseParameter</t>
+    <t>ResponseParameter</t>
   </si>
   <si>
     <t>queryDBSql</t>
@@ -96,49 +96,19 @@
     <t>post</t>
   </si>
   <si>
-    <t>http://10.243.141.100</t>
-  </si>
-  <si>
     <t>/secu</t>
   </si>
   <si>
     <t>application/x-www-form-urlencoded;charset=UTF-8</t>
   </si>
   <si>
-    <t>data={
-    "userId":"143374",
-    "PASSWORD":"qwer1234",
-    "f":"SECU_Login"
-}</t>
-  </si>
-  <si>
     <t>token</t>
   </si>
   <si>
-    <t>获取【小小测试001】客户信息</t>
+    <t>n</t>
   </si>
   <si>
     <t>/irs</t>
-  </si>
-  <si>
-    <t>data={
-    "PRODUCT": "*",
-    "CUSTOMER_ID": "",
-    "ACCOUNT_NO": "",
-    "MARGIN_NO": "",
-    "CUSTOMER_NAME_CH": "小小测试001",
-    "SIGN_STATUS": "*",
-    "CUSTOMER_STATUS": "*",
-    "MARGIN_STATUS": "*",
-    "LOCALSYS_ID": "",
-    "page_NO": 1,
-    "page_count": 10,
-    "tableDataID": "GETDATA_IRS_CUSTOMER_SIGN",
-    "f": "FRAM_GetTableDataList",
-    "u": "143374",
-    "l": "${token}",
-    "e": "999"
-}</t>
   </si>
   <si>
     <t>CLRBLQR</t>
@@ -435,6 +405,9 @@
   </si>
   <si>
     <t>（不等于约定值）</t>
+  </si>
+  <si>
+    <t>获取客户信息</t>
   </si>
 </sst>
 </file>
@@ -976,25 +949,19 @@
       <c r="G2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="I2" s="13">
-        <v>9192</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="K2" s="11"/>
       <c r="L2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>27</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M2" s="12"/>
       <c r="N2" s="11"/>
       <c r="O2" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P2" s="12"/>
       <c r="Q2" s="11"/>
@@ -1002,31 +969,24 @@
     </row>
     <row r="3" spans="1:18" ht="19.95" customHeight="1">
       <c r="D3" s="11" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="13">
-        <v>9192</v>
-      </c>
+      <c r="I3" s="13"/>
       <c r="J3" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K3" s="11"/>
       <c r="L3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>31</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M3" s="12"/>
       <c r="N3" s="14"/>
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
@@ -1049,59 +1009,59 @@
   <sheetData>
     <row r="1" spans="1:3" ht="45" customHeight="1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" customHeight="1">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" customHeight="1">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1">
@@ -1136,197 +1096,197 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="D4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="D5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="D8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="D11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="D12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="D15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="7:9">
       <c r="G24" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="7:9">
       <c r="G25" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="7:9">
       <c r="G26" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="7:9">
       <c r="G27" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="7:9">
       <c r="G28" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="7:9">
       <c r="G29" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I29" s="1"/>
     </row>
     <row r="30" spans="7:9">
       <c r="G30" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="7:9">
       <c r="G31" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="7:9">
       <c r="G32" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/code/api-autotest-tool/case/case.xlsx
+++ b/code/api-autotest-tool/case/case.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sauro\Desktop\REPO\pw-z.github.io\code\api-autotest-tool\case\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2087\Desktop\REPO\pw-z.github.io\code\api-autotest-tool\case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F78635-8C61-4C36-BE0E-9EF16F1B6E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB021D82-2BB7-4435-A439-DA57587AA49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="353" windowWidth="20715" windowHeight="13424" tabRatio="780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="30936" windowHeight="17040" tabRatio="780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="9" r:id="rId1"/>
@@ -73,9 +73,6 @@
     <t>ExpectedDQLData</t>
   </si>
   <si>
-    <t>sqlParameter1</t>
-  </si>
-  <si>
     <t>BASE</t>
   </si>
   <si>
@@ -97,10 +94,13 @@
     <t>application/x-www-form-urlencoded;charset=UTF-8</t>
   </si>
   <si>
-    <t>token</t>
-  </si>
-  <si>
-    <t>SELECT * FROM BASE_PARAM</t>
+    <t>token:token233</t>
+  </si>
+  <si>
+    <t>SELECT count(*) FROM BASE_PARAM</t>
+  </si>
+  <si>
+    <t>32</t>
   </si>
   <si>
     <t>信息获取</t>
@@ -222,7 +222,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -250,20 +250,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -273,7 +276,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -580,24 +583,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" customWidth="1"/>
-    <col min="2" max="2" width="12.86328125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="3" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="47.1328125" customWidth="1"/>
-    <col min="5" max="7" width="10.46484375" customWidth="1"/>
-    <col min="8" max="8" width="23.796875" customWidth="1"/>
+    <col min="4" max="4" width="47.109375" customWidth="1"/>
+    <col min="5" max="7" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.77734375" customWidth="1"/>
     <col min="9" max="9" width="5.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.46484375" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="52.6640625" customWidth="1"/>
     <col min="13" max="13" width="43.33203125" customWidth="1"/>
-    <col min="14" max="18" width="26.46484375" customWidth="1"/>
+    <col min="14" max="16" width="26.44140625" customWidth="1"/>
+    <col min="17" max="17" width="26.44140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="27" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -649,54 +653,52 @@
       <c r="Q1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:17" s="2" customFormat="1" ht="64.95" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" s="2" customFormat="1" ht="65" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="B2" s="10">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="9">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="E2" s="7">
         <v>111</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H2"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="7"/>
       <c r="O2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="Q2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
     </row>
-    <row r="3" spans="1:18" ht="72" customHeight="1">
-      <c r="A3" s="15"/>
+    <row r="3" spans="1:17" ht="72" customHeight="1">
+      <c r="A3" s="16"/>
       <c r="B3" s="3">
         <v>2</v>
       </c>
@@ -711,9 +713,9 @@
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="10"/>
+        <v>20</v>
+      </c>
+      <c r="I3" s="9"/>
       <c r="J3" s="7" t="s">
         <v>29</v>
       </c>
@@ -721,7 +723,7 @@
         <v>30</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="11" t="s">
@@ -730,7 +732,6 @@
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
